--- a/StructureDefinition-mii-pr-molgen-anforderung-genetischer-test.xlsx
+++ b/StructureDefinition-mii-pr-molgen-anforderung-genetischer-test.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T14:33:36+00:00</t>
+    <t>2026-09-13T11:19:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-molgen-anforderung-genetischer-test.xlsx
+++ b/StructureDefinition-mii-pr-molgen-anforderung-genetischer-test.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T11:19:28+00:00</t>
+    <t>2026-09-13T17:10:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
